--- a/data/GreatLink/Dynamic Balanced Portfolio.xlsx
+++ b/data/GreatLink/Dynamic Balanced Portfolio.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="PriceHistory" sheetId="1" r:id="GemRid596733"/>
+    <sheet name="PriceHistory" sheetId="1" r:id="GemRid95150"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
   <si>
     <t>Price Date</t>
   </si>
@@ -26,27 +26,105 @@
     <t>Currency - Unit Level</t>
   </si>
   <si>
+    <t>27/02/2026</t>
+  </si>
+  <si>
+    <t>0.957</t>
+  </si>
+  <si>
+    <t>SGD</t>
+  </si>
+  <si>
+    <t>26/02/2026</t>
+  </si>
+  <si>
+    <t>25/02/2026</t>
+  </si>
+  <si>
+    <t>0.958</t>
+  </si>
+  <si>
+    <t>24/02/2026</t>
+  </si>
+  <si>
+    <t>0.955</t>
+  </si>
+  <si>
+    <t>23/02/2026</t>
+  </si>
+  <si>
+    <t>0.950</t>
+  </si>
+  <si>
+    <t>20/02/2026</t>
+  </si>
+  <si>
+    <t>19/02/2026</t>
+  </si>
+  <si>
+    <t>0.952</t>
+  </si>
+  <si>
+    <t>16/02/2026</t>
+  </si>
+  <si>
+    <t>0.947</t>
+  </si>
+  <si>
+    <t>13/02/2026</t>
+  </si>
+  <si>
+    <t>0.946</t>
+  </si>
+  <si>
+    <t>12/02/2026</t>
+  </si>
+  <si>
+    <t>11/02/2026</t>
+  </si>
+  <si>
+    <t>0.953</t>
+  </si>
+  <si>
+    <t>10/02/2026</t>
+  </si>
+  <si>
+    <t>0.954</t>
+  </si>
+  <si>
+    <t>09/02/2026</t>
+  </si>
+  <si>
+    <t>06/02/2026</t>
+  </si>
+  <si>
+    <t>05/02/2026</t>
+  </si>
+  <si>
+    <t>0.942</t>
+  </si>
+  <si>
+    <t>04/02/2026</t>
+  </si>
+  <si>
+    <t>0.948</t>
+  </si>
+  <si>
+    <t>03/02/2026</t>
+  </si>
+  <si>
+    <t>0.949</t>
+  </si>
+  <si>
     <t>02/02/2026</t>
   </si>
   <si>
-    <t>0.954</t>
-  </si>
-  <si>
-    <t>SGD</t>
-  </si>
-  <si>
     <t>30/01/2026</t>
   </si>
   <si>
-    <t>0.952</t>
-  </si>
-  <si>
     <t>29/01/2026</t>
   </si>
   <si>
-    <t>0.955</t>
-  </si>
-  <si>
     <t>28/01/2026</t>
   </si>
   <si>
@@ -59,9 +137,6 @@
     <t>23/01/2026</t>
   </si>
   <si>
-    <t>0.953</t>
-  </si>
-  <si>
     <t>22/01/2026</t>
   </si>
   <si>
@@ -74,15 +149,9 @@
     <t>20/01/2026</t>
   </si>
   <si>
-    <t>0.947</t>
-  </si>
-  <si>
     <t>19/01/2026</t>
   </si>
   <si>
-    <t>0.958</t>
-  </si>
-  <si>
     <t>16/01/2026</t>
   </si>
   <si>
@@ -134,9 +203,6 @@
     <t>30/12/2025</t>
   </si>
   <si>
-    <t>0.946</t>
-  </si>
-  <si>
     <t>29/12/2025</t>
   </si>
   <si>
@@ -158,9 +224,6 @@
     <t>19/12/2025</t>
   </si>
   <si>
-    <t>0.942</t>
-  </si>
-  <si>
     <t>18/12/2025</t>
   </si>
   <si>
@@ -269,9 +332,6 @@
     <t>13/11/2025</t>
   </si>
   <si>
-    <t>0.948</t>
-  </si>
-  <si>
     <t>12/11/2025</t>
   </si>
   <si>
@@ -320,9 +380,6 @@
     <t>23/10/2025</t>
   </si>
   <si>
-    <t>0.949</t>
-  </si>
-  <si>
     <t>22/10/2025</t>
   </si>
   <si>
@@ -336,9 +393,6 @@
   </si>
   <si>
     <t>15/10/2025</t>
-  </si>
-  <si>
-    <t>0.950</t>
   </si>
 </sst>
 </file>
@@ -691,7 +745,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -699,10 +753,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -710,10 +764,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
         <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -724,7 +778,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -732,10 +786,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -743,10 +797,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -754,10 +808,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -765,10 +819,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -776,10 +830,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -787,10 +841,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -798,10 +852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
         <v>5</v>
@@ -809,10 +863,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
         <v>24</v>
-      </c>
-      <c r="B14" t="s">
-        <v>23</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -820,10 +874,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -831,10 +885,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -842,10 +896,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
@@ -853,10 +907,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
         <v>5</v>
@@ -864,10 +918,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -875,10 +929,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -886,10 +940,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -897,10 +951,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
@@ -908,10 +962,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -919,10 +973,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
         <v>5</v>
@@ -930,10 +984,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
         <v>5</v>
@@ -944,7 +998,7 @@
         <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
@@ -955,7 +1009,7 @@
         <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C27" t="s">
         <v>5</v>
@@ -963,10 +1017,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="C28" t="s">
         <v>5</v>
@@ -974,10 +1028,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
@@ -988,7 +1042,7 @@
         <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C30" t="s">
         <v>5</v>
@@ -996,10 +1050,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" t="s">
         <v>46</v>
-      </c>
-      <c r="B31" t="s">
-        <v>47</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
@@ -1010,7 +1064,7 @@
         <v>48</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -1018,10 +1072,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" t="s">
         <v>50</v>
-      </c>
-      <c r="B33" t="s">
-        <v>51</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -1029,10 +1083,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -1040,10 +1094,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -1051,10 +1105,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -1062,10 +1116,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B37" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
@@ -1073,10 +1127,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B38" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
@@ -1084,10 +1138,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="C39" t="s">
         <v>5</v>
@@ -1095,10 +1149,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="C40" t="s">
         <v>5</v>
@@ -1106,10 +1160,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B41" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
         <v>5</v>
@@ -1117,10 +1171,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B42" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C42" t="s">
         <v>5</v>
@@ -1128,10 +1182,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B43" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C43" t="s">
         <v>5</v>
@@ -1139,10 +1193,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
@@ -1150,10 +1204,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="C45" t="s">
         <v>5</v>
@@ -1161,10 +1215,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B46" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="C46" t="s">
         <v>5</v>
@@ -1172,10 +1226,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C47" t="s">
         <v>5</v>
@@ -1183,10 +1237,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B48" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="C48" t="s">
         <v>5</v>
@@ -1194,10 +1248,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B49" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C49" t="s">
         <v>5</v>
@@ -1205,10 +1259,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B50" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="C50" t="s">
         <v>5</v>
@@ -1216,10 +1270,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>73</v>
+      </c>
+      <c r="B51" t="s">
         <v>74</v>
-      </c>
-      <c r="B51" t="s">
-        <v>75</v>
       </c>
       <c r="C51" t="s">
         <v>5</v>
@@ -1227,10 +1281,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
+        <v>75</v>
+      </c>
+      <c r="B52" t="s">
         <v>76</v>
-      </c>
-      <c r="B52" t="s">
-        <v>77</v>
       </c>
       <c r="C52" t="s">
         <v>5</v>
@@ -1238,10 +1292,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
+        <v>77</v>
+      </c>
+      <c r="B53" t="s">
         <v>78</v>
-      </c>
-      <c r="B53" t="s">
-        <v>79</v>
       </c>
       <c r="C53" t="s">
         <v>5</v>
@@ -1249,10 +1303,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B54" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C54" t="s">
         <v>5</v>
@@ -1260,10 +1314,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="C55" t="s">
         <v>5</v>
@@ -1271,10 +1325,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B56" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C56" t="s">
         <v>5</v>
@@ -1282,10 +1336,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B57" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="C57" t="s">
         <v>5</v>
@@ -1293,10 +1347,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B58" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C58" t="s">
         <v>5</v>
@@ -1304,10 +1358,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B59" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C59" t="s">
         <v>5</v>
@@ -1315,10 +1369,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B60" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="C60" t="s">
         <v>5</v>
@@ -1326,10 +1380,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B61" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="C61" t="s">
         <v>5</v>
@@ -1337,10 +1391,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B62" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C62" t="s">
         <v>5</v>
@@ -1348,10 +1402,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B63" t="s">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="C63" t="s">
         <v>5</v>
@@ -1359,10 +1413,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B64" t="s">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="C64" t="s">
         <v>5</v>
@@ -1370,10 +1424,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B65" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="C65" t="s">
         <v>5</v>
@@ -1381,10 +1435,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>92</v>
+      </c>
+      <c r="B66" t="s">
         <v>93</v>
-      </c>
-      <c r="B66" t="s">
-        <v>94</v>
       </c>
       <c r="C66" t="s">
         <v>5</v>
@@ -1392,10 +1446,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B67" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="C67" t="s">
         <v>5</v>
@@ -1403,10 +1457,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>95</v>
+      </c>
+      <c r="B68" t="s">
         <v>96</v>
-      </c>
-      <c r="B68" t="s">
-        <v>21</v>
       </c>
       <c r="C68" t="s">
         <v>5</v>
@@ -1417,7 +1471,7 @@
         <v>97</v>
       </c>
       <c r="B69" t="s">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="C69" t="s">
         <v>5</v>
@@ -1425,10 +1479,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B70" t="s">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="C70" t="s">
         <v>5</v>
@@ -1436,10 +1490,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B71" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="C71" t="s">
         <v>5</v>
@@ -1447,10 +1501,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B72" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="C72" t="s">
         <v>5</v>
@@ -1458,10 +1512,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B73" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="C73" t="s">
         <v>5</v>
@@ -1469,10 +1523,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B74" t="s">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="C74" t="s">
         <v>5</v>
@@ -1480,10 +1534,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B75" t="s">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="C75" t="s">
         <v>5</v>
@@ -1491,10 +1545,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B76" t="s">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="C76" t="s">
         <v>5</v>
@@ -1502,12 +1556,199 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B77" t="s">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="C77" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>108</v>
+      </c>
+      <c r="B78" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>109</v>
+      </c>
+      <c r="B79" t="s">
+        <v>30</v>
+      </c>
+      <c r="C79" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>110</v>
+      </c>
+      <c r="B80" t="s">
+        <v>15</v>
+      </c>
+      <c r="C80" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>111</v>
+      </c>
+      <c r="B81" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>112</v>
+      </c>
+      <c r="B82" t="s">
+        <v>53</v>
+      </c>
+      <c r="C82" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>113</v>
+      </c>
+      <c r="B83" t="s">
+        <v>114</v>
+      </c>
+      <c r="C83" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>115</v>
+      </c>
+      <c r="B84" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>116</v>
+      </c>
+      <c r="B85" t="s">
+        <v>8</v>
+      </c>
+      <c r="C85" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>117</v>
+      </c>
+      <c r="B86" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>118</v>
+      </c>
+      <c r="B87" t="s">
+        <v>53</v>
+      </c>
+      <c r="C87" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>119</v>
+      </c>
+      <c r="B88" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>120</v>
+      </c>
+      <c r="B89" t="s">
+        <v>32</v>
+      </c>
+      <c r="C89" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>121</v>
+      </c>
+      <c r="B90" t="s">
+        <v>19</v>
+      </c>
+      <c r="C90" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>122</v>
+      </c>
+      <c r="B91" t="s">
+        <v>30</v>
+      </c>
+      <c r="C91" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>123</v>
+      </c>
+      <c r="B92" t="s">
+        <v>32</v>
+      </c>
+      <c r="C92" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>124</v>
+      </c>
+      <c r="B93" t="s">
+        <v>32</v>
+      </c>
+      <c r="C93" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>125</v>
+      </c>
+      <c r="B94" t="s">
+        <v>12</v>
+      </c>
+      <c r="C94" t="s">
         <v>5</v>
       </c>
     </row>

--- a/data/GreatLink/Dynamic Balanced Portfolio.xlsx
+++ b/data/GreatLink/Dynamic Balanced Portfolio.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="PriceHistory" sheetId="1" r:id="GemRid95150"/>
+    <sheet name="PriceHistory" sheetId="1" r:id="GemRid678028"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
   <si>
     <t>Price Date</t>
   </si>
@@ -26,24 +26,177 @@
     <t>Currency - Unit Level</t>
   </si>
   <si>
+    <t>09/04/2026</t>
+  </si>
+  <si>
+    <t>0.941</t>
+  </si>
+  <si>
+    <t>SGD</t>
+  </si>
+  <si>
+    <t>08/04/2026</t>
+  </si>
+  <si>
+    <t>07/04/2026</t>
+  </si>
+  <si>
+    <t>0.925</t>
+  </si>
+  <si>
+    <t>06/04/2026</t>
+  </si>
+  <si>
+    <t>0.923</t>
+  </si>
+  <si>
+    <t>02/04/2026</t>
+  </si>
+  <si>
+    <t>0.921</t>
+  </si>
+  <si>
+    <t>01/04/2026</t>
+  </si>
+  <si>
+    <t>31/03/2026</t>
+  </si>
+  <si>
+    <t>0.915</t>
+  </si>
+  <si>
+    <t>30/03/2026</t>
+  </si>
+  <si>
+    <t>0.903</t>
+  </si>
+  <si>
+    <t>27/03/2026</t>
+  </si>
+  <si>
+    <t>0.904</t>
+  </si>
+  <si>
+    <t>26/03/2026</t>
+  </si>
+  <si>
+    <t>0.912</t>
+  </si>
+  <si>
+    <t>25/03/2026</t>
+  </si>
+  <si>
+    <t>0.922</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>0.916</t>
+  </si>
+  <si>
+    <t>23/03/2026</t>
+  </si>
+  <si>
+    <t>0.914</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>0.917</t>
+  </si>
+  <si>
+    <t>19/03/2026</t>
+  </si>
+  <si>
+    <t>0.924</t>
+  </si>
+  <si>
+    <t>18/03/2026</t>
+  </si>
+  <si>
+    <t>0.931</t>
+  </si>
+  <si>
+    <t>17/03/2026</t>
+  </si>
+  <si>
+    <t>0.933</t>
+  </si>
+  <si>
+    <t>16/03/2026</t>
+  </si>
+  <si>
+    <t>13/03/2026</t>
+  </si>
+  <si>
+    <t>0.929</t>
+  </si>
+  <si>
+    <t>12/03/2026</t>
+  </si>
+  <si>
+    <t>0.932</t>
+  </si>
+  <si>
+    <t>11/03/2026</t>
+  </si>
+  <si>
+    <t>0.938</t>
+  </si>
+  <si>
+    <t>10/03/2026</t>
+  </si>
+  <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
+    <t>0.936</t>
+  </si>
+  <si>
+    <t>06/03/2026</t>
+  </si>
+  <si>
+    <t>0.940</t>
+  </si>
+  <si>
+    <t>05/03/2026</t>
+  </si>
+  <si>
+    <t>0.946</t>
+  </si>
+  <si>
+    <t>04/03/2026</t>
+  </si>
+  <si>
+    <t>0.945</t>
+  </si>
+  <si>
+    <t>03/03/2026</t>
+  </si>
+  <si>
+    <t>0.947</t>
+  </si>
+  <si>
+    <t>02/03/2026</t>
+  </si>
+  <si>
+    <t>0.958</t>
+  </si>
+  <si>
     <t>27/02/2026</t>
   </si>
   <si>
     <t>0.957</t>
   </si>
   <si>
-    <t>SGD</t>
-  </si>
-  <si>
     <t>26/02/2026</t>
   </si>
   <si>
     <t>25/02/2026</t>
   </si>
   <si>
-    <t>0.958</t>
-  </si>
-  <si>
     <t>24/02/2026</t>
   </si>
   <si>
@@ -68,15 +221,9 @@
     <t>16/02/2026</t>
   </si>
   <si>
-    <t>0.947</t>
-  </si>
-  <si>
     <t>13/02/2026</t>
   </si>
   <si>
-    <t>0.946</t>
-  </si>
-  <si>
     <t>12/02/2026</t>
   </si>
   <si>
@@ -215,9 +362,6 @@
     <t>23/12/2025</t>
   </si>
   <si>
-    <t>0.945</t>
-  </si>
-  <si>
     <t>22/12/2025</t>
   </si>
   <si>
@@ -227,15 +371,9 @@
     <t>18/12/2025</t>
   </si>
   <si>
-    <t>0.936</t>
-  </si>
-  <si>
     <t>17/12/2025</t>
   </si>
   <si>
-    <t>0.933</t>
-  </si>
-  <si>
     <t>16/12/2025</t>
   </si>
   <si>
@@ -251,9 +389,6 @@
     <t>12/12/2025</t>
   </si>
   <si>
-    <t>0.941</t>
-  </si>
-  <si>
     <t>11/12/2025</t>
   </si>
   <si>
@@ -296,22 +431,13 @@
     <t>25/11/2025</t>
   </si>
   <si>
-    <t>0.940</t>
-  </si>
-  <si>
     <t>24/11/2025</t>
   </si>
   <si>
     <t>21/11/2025</t>
   </si>
   <si>
-    <t>0.932</t>
-  </si>
-  <si>
     <t>20/11/2025</t>
-  </si>
-  <si>
-    <t>0.931</t>
   </si>
   <si>
     <t>19/11/2025</t>
@@ -833,7 +959,7 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -841,10 +967,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -852,10 +978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
         <v>5</v>
@@ -863,10 +989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -874,10 +1000,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -885,10 +1011,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -896,10 +1022,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
@@ -907,10 +1033,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
         <v>5</v>
@@ -918,10 +1044,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
         <v>33</v>
-      </c>
-      <c r="B19" t="s">
-        <v>24</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -929,10 +1055,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -940,10 +1066,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -951,10 +1077,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
@@ -962,10 +1088,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -973,10 +1099,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
         <v>5</v>
@@ -984,10 +1110,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s">
         <v>5</v>
@@ -995,10 +1121,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
@@ -1006,10 +1132,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s">
         <v>5</v>
@@ -1017,10 +1143,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="C28" t="s">
         <v>5</v>
@@ -1028,10 +1154,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
@@ -1039,10 +1165,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C30" t="s">
         <v>5</v>
@@ -1050,10 +1176,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
@@ -1061,10 +1187,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -1072,10 +1198,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -1083,10 +1209,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -1094,10 +1220,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -1105,10 +1231,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -1116,10 +1242,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
@@ -1127,10 +1253,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
@@ -1138,10 +1264,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
         <v>5</v>
@@ -1149,10 +1275,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B40" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="C40" t="s">
         <v>5</v>
@@ -1160,10 +1286,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B41" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C41" t="s">
         <v>5</v>
@@ -1171,10 +1297,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="B42" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="C42" t="s">
         <v>5</v>
@@ -1182,10 +1308,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B43" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="C43" t="s">
         <v>5</v>
@@ -1193,10 +1319,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="B44" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
@@ -1204,10 +1330,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="B45" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="C45" t="s">
         <v>5</v>
@@ -1215,10 +1341,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B46" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C46" t="s">
         <v>5</v>
@@ -1226,10 +1352,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C47" t="s">
         <v>5</v>
@@ -1237,10 +1363,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="B48" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="C48" t="s">
         <v>5</v>
@@ -1248,10 +1374,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B49" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C49" t="s">
         <v>5</v>
@@ -1259,10 +1385,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="B50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C50" t="s">
         <v>5</v>
@@ -1270,10 +1396,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>86</v>
+      </c>
+      <c r="B51" t="s">
         <v>73</v>
-      </c>
-      <c r="B51" t="s">
-        <v>74</v>
       </c>
       <c r="C51" t="s">
         <v>5</v>
@@ -1281,10 +1407,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="B52" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C52" t="s">
         <v>5</v>
@@ -1292,10 +1418,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B53" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C53" t="s">
         <v>5</v>
@@ -1303,10 +1429,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B54" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C54" t="s">
         <v>5</v>
@@ -1314,10 +1440,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B55" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="C55" t="s">
         <v>5</v>
@@ -1325,10 +1451,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C56" t="s">
         <v>5</v>
@@ -1336,10 +1462,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B57" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="C57" t="s">
         <v>5</v>
@@ -1347,10 +1473,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="B58" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="C58" t="s">
         <v>5</v>
@@ -1358,10 +1484,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B59" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="C59" t="s">
         <v>5</v>
@@ -1369,10 +1495,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C60" t="s">
         <v>5</v>
@@ -1380,10 +1506,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B61" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="C61" t="s">
         <v>5</v>
@@ -1391,10 +1517,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="C62" t="s">
         <v>5</v>
@@ -1402,10 +1528,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="B63" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="C63" t="s">
         <v>5</v>
@@ -1413,10 +1539,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B64" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C64" t="s">
         <v>5</v>
@@ -1424,10 +1550,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B65" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C65" t="s">
         <v>5</v>
@@ -1435,10 +1561,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B66" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="C66" t="s">
         <v>5</v>
@@ -1446,10 +1572,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B67" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C67" t="s">
         <v>5</v>
@@ -1457,10 +1583,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B68" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="C68" t="s">
         <v>5</v>
@@ -1468,10 +1594,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B69" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="C69" t="s">
         <v>5</v>
@@ -1479,10 +1605,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B70" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="C70" t="s">
         <v>5</v>
@@ -1490,10 +1616,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B71" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="C71" t="s">
         <v>5</v>
@@ -1501,10 +1627,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B72" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="C72" t="s">
         <v>5</v>
@@ -1512,10 +1638,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B73" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="C73" t="s">
         <v>5</v>
@@ -1523,10 +1649,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B74" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="C74" t="s">
         <v>5</v>
@@ -1534,10 +1660,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B75" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="C75" t="s">
         <v>5</v>
@@ -1545,10 +1671,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B76" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="C76" t="s">
         <v>5</v>
@@ -1556,10 +1682,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="B77" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C77" t="s">
         <v>5</v>
@@ -1567,10 +1693,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="B78" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="C78" t="s">
         <v>5</v>
@@ -1578,10 +1704,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B79" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="C79" t="s">
         <v>5</v>
@@ -1589,10 +1715,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="B80" t="s">
-        <v>15</v>
+        <v>122</v>
       </c>
       <c r="C80" t="s">
         <v>5</v>
@@ -1600,10 +1726,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="B81" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C81" t="s">
         <v>5</v>
@@ -1611,10 +1737,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B82" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C82" t="s">
         <v>5</v>
@@ -1622,10 +1748,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B83" t="s">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="C83" t="s">
         <v>5</v>
@@ -1633,10 +1759,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B84" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="C84" t="s">
         <v>5</v>
@@ -1644,10 +1770,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B85" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="C85" t="s">
         <v>5</v>
@@ -1655,10 +1781,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B86" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="C86" t="s">
         <v>5</v>
@@ -1666,10 +1792,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B87" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C87" t="s">
         <v>5</v>
@@ -1677,10 +1803,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B88" t="s">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="C88" t="s">
         <v>5</v>
@@ -1688,10 +1814,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B89" t="s">
-        <v>32</v>
+        <v>109</v>
       </c>
       <c r="C89" t="s">
         <v>5</v>
@@ -1699,10 +1825,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B90" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C90" t="s">
         <v>5</v>
@@ -1710,10 +1836,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B91" t="s">
-        <v>30</v>
+        <v>109</v>
       </c>
       <c r="C91" t="s">
         <v>5</v>
@@ -1721,10 +1847,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B92" t="s">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="C92" t="s">
         <v>5</v>
@@ -1732,10 +1858,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B93" t="s">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="C93" t="s">
         <v>5</v>
@@ -1743,12 +1869,320 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="B94" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="C94" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>138</v>
+      </c>
+      <c r="B95" t="s">
+        <v>120</v>
+      </c>
+      <c r="C95" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>139</v>
+      </c>
+      <c r="B96" t="s">
+        <v>40</v>
+      </c>
+      <c r="C96" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>140</v>
+      </c>
+      <c r="B97" t="s">
+        <v>33</v>
+      </c>
+      <c r="C97" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>141</v>
+      </c>
+      <c r="B98" t="s">
+        <v>142</v>
+      </c>
+      <c r="C98" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>143</v>
+      </c>
+      <c r="B99" t="s">
+        <v>35</v>
+      </c>
+      <c r="C99" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>144</v>
+      </c>
+      <c r="B100" t="s">
+        <v>4</v>
+      </c>
+      <c r="C100" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>145</v>
+      </c>
+      <c r="B101" t="s">
+        <v>135</v>
+      </c>
+      <c r="C101" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>146</v>
+      </c>
+      <c r="B102" t="s">
+        <v>79</v>
+      </c>
+      <c r="C102" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>147</v>
+      </c>
+      <c r="B103" t="s">
+        <v>61</v>
+      </c>
+      <c r="C103" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>148</v>
+      </c>
+      <c r="B104" t="s">
+        <v>71</v>
+      </c>
+      <c r="C104" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>149</v>
+      </c>
+      <c r="B105" t="s">
+        <v>71</v>
+      </c>
+      <c r="C105" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>150</v>
+      </c>
+      <c r="B106" t="s">
+        <v>109</v>
+      </c>
+      <c r="C106" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>151</v>
+      </c>
+      <c r="B107" t="s">
+        <v>79</v>
+      </c>
+      <c r="C107" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>152</v>
+      </c>
+      <c r="B108" t="s">
+        <v>66</v>
+      </c>
+      <c r="C108" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>153</v>
+      </c>
+      <c r="B109" t="s">
+        <v>66</v>
+      </c>
+      <c r="C109" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>154</v>
+      </c>
+      <c r="B110" t="s">
+        <v>102</v>
+      </c>
+      <c r="C110" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>155</v>
+      </c>
+      <c r="B111" t="s">
+        <v>156</v>
+      </c>
+      <c r="C111" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>157</v>
+      </c>
+      <c r="B112" t="s">
+        <v>61</v>
+      </c>
+      <c r="C112" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>158</v>
+      </c>
+      <c r="B113" t="s">
+        <v>55</v>
+      </c>
+      <c r="C113" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>159</v>
+      </c>
+      <c r="B114" t="s">
+        <v>55</v>
+      </c>
+      <c r="C114" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>160</v>
+      </c>
+      <c r="B115" t="s">
+        <v>102</v>
+      </c>
+      <c r="C115" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>161</v>
+      </c>
+      <c r="B116" t="s">
+        <v>66</v>
+      </c>
+      <c r="C116" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>162</v>
+      </c>
+      <c r="B117" t="s">
+        <v>81</v>
+      </c>
+      <c r="C117" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>163</v>
+      </c>
+      <c r="B118" t="s">
+        <v>49</v>
+      </c>
+      <c r="C118" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>164</v>
+      </c>
+      <c r="B119" t="s">
+        <v>79</v>
+      </c>
+      <c r="C119" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>165</v>
+      </c>
+      <c r="B120" t="s">
+        <v>81</v>
+      </c>
+      <c r="C120" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>166</v>
+      </c>
+      <c r="B121" t="s">
+        <v>81</v>
+      </c>
+      <c r="C121" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>167</v>
+      </c>
+      <c r="B122" t="s">
+        <v>63</v>
+      </c>
+      <c r="C122" t="s">
         <v>5</v>
       </c>
     </row>
